--- a/artfynd/A 11879-2023 artfynd.xlsx
+++ b/artfynd/A 11879-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133713369</v>
       </c>
       <c r="B2" t="n">
-        <v>57952</v>
+        <v>57959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133713460</v>
       </c>
       <c r="B3" t="n">
-        <v>58358</v>
+        <v>58365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11879-2023 artfynd.xlsx
+++ b/artfynd/A 11879-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133713369</v>
       </c>
       <c r="B2" t="n">
-        <v>57959</v>
+        <v>57969</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133713460</v>
       </c>
       <c r="B3" t="n">
-        <v>58365</v>
+        <v>58375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11879-2023 artfynd.xlsx
+++ b/artfynd/A 11879-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,129 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133713461</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58375</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Backen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>382766</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6420713</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Herrljunga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Molla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11879-2023 artfynd.xlsx
+++ b/artfynd/A 11879-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713369</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713460</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,8 +1052,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133713461</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>